--- a/naver_webtoon_one_title_final_v4/해피 페이스_회차정보.xlsx
+++ b/naver_webtoon_one_title_final_v4/해피 페이스_회차정보.xlsx
@@ -570,10 +570,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>3275</v>
+        <v>3305</v>
       </c>
       <c r="L2" t="n">
-        <v>3743</v>
+        <v>3768</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -582,12 +582,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:12.634947</t>
+          <t>2026-06-27 01:32:02.250584</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:18.479013</t>
+          <t>2026-06-27 01:32:06.539056</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -653,10 +653,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2399</v>
+        <v>2425</v>
       </c>
       <c r="L3" t="n">
-        <v>2484</v>
+        <v>2500</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -665,12 +665,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:12.634947</t>
+          <t>2026-06-27 01:32:02.250584</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:26.900749</t>
+          <t>2026-06-27 01:32:13.290695</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -736,10 +736,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2436</v>
+        <v>2460</v>
       </c>
       <c r="L4" t="n">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -748,12 +748,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:12.634947</t>
+          <t>2026-06-27 01:32:02.250584</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:06:32.417140</t>
+          <t>2026-06-27 01:32:20.840880</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -815,10 +815,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2545</v>
+        <v>2568</v>
       </c>
       <c r="L5" t="n">
-        <v>2573</v>
+        <v>2588</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>46178.12961561353</v>
+        <v>46200.06420934334</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="L6" t="n">
-        <v>2414</v>
+        <v>2429</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46178.12968377008</v>
+        <v>46200.06426321106</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         <v>9.98</v>
       </c>
       <c r="K7" t="n">
-        <v>2432</v>
+        <v>2459</v>
       </c>
       <c r="L7" t="n">
-        <v>2431</v>
+        <v>2447</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46178.12975064296</v>
+        <v>46200.06432495129</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         <v>9.98</v>
       </c>
       <c r="K8" t="n">
-        <v>2259</v>
+        <v>2282</v>
       </c>
       <c r="L8" t="n">
-        <v>2327</v>
+        <v>2343</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46178.12980891136</v>
+        <v>46200.06438474558</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2526</v>
+        <v>2551</v>
       </c>
       <c r="L9" t="n">
-        <v>2411</v>
+        <v>2431</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>46178.12986697446</v>
+        <v>46200.0644522807</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>2017</v>
+        <v>2038</v>
       </c>
       <c r="L10" t="n">
-        <v>2088</v>
+        <v>2106</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46178.12993255698</v>
+        <v>46200.06452693709</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
         <v>9.98</v>
       </c>
       <c r="K11" t="n">
-        <v>2034</v>
+        <v>2059</v>
       </c>
       <c r="L11" t="n">
-        <v>2077</v>
+        <v>2096</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46178.12998889307</v>
+        <v>46200.06458519953</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1351,13 +1351,13 @@
         <v>45843.91666666666</v>
       </c>
       <c r="J12" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="K12" t="n">
-        <v>2035</v>
+        <v>2058</v>
       </c>
       <c r="L12" t="n">
-        <v>2081</v>
+        <v>2097</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46178.13004117905</v>
+        <v>46200.06464770166</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>11화 - 망명광대의 추격
 별점
-9.97
+9.98
 25.07.06</t>
         </is>
       </c>
@@ -1431,10 +1431,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1929</v>
+        <v>1953</v>
       </c>
       <c r="L13" t="n">
-        <v>1958</v>
+        <v>1975</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46178.13009269632</v>
+        <v>46200.06470479975</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2390</v>
+        <v>2416</v>
       </c>
       <c r="L14" t="n">
-        <v>2266</v>
+        <v>2283</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>46178.13015076029</v>
+        <v>46200.06476229006</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>2025</v>
+        <v>2051</v>
       </c>
       <c r="L15" t="n">
-        <v>1995</v>
+        <v>2015</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46178.13020862798</v>
+        <v>46200.06482304884</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>2272</v>
+        <v>2298</v>
       </c>
       <c r="L16" t="n">
-        <v>2116</v>
+        <v>2133</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46178.13025801315</v>
+        <v>46200.06488285292</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>2071</v>
+        <v>2096</v>
       </c>
       <c r="L17" t="n">
-        <v>2034</v>
+        <v>2054</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46178.1303203233</v>
+        <v>46200.06494998345</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>2035</v>
+        <v>2062</v>
       </c>
       <c r="L18" t="n">
-        <v>1942</v>
+        <v>1959</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>46178.12931290448</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46178.13037297739</v>
+        <v>46200.06501037824</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>2074</v>
+        <v>2096</v>
       </c>
       <c r="L19" t="n">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46178.13043221752</v>
+        <v>46200.06507134403</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>9.98</v>
       </c>
       <c r="K20" t="n">
-        <v>2204</v>
+        <v>2230</v>
       </c>
       <c r="L20" t="n">
-        <v>2026</v>
+        <v>2043</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46178.13049008424</v>
+        <v>46200.06513540713</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1929</v>
+        <v>1954</v>
       </c>
       <c r="L21" t="n">
-        <v>1808</v>
+        <v>1827</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06391493732</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46178.130551184</v>
+        <v>46200.06520793567</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         <v>9.98</v>
       </c>
       <c r="K22" t="n">
-        <v>2358</v>
+        <v>2384</v>
       </c>
       <c r="L22" t="n">
-        <v>2040</v>
+        <v>2060</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>46178.13060387734</v>
+        <v>46200.06526485461</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>2214</v>
+        <v>2243</v>
       </c>
       <c r="L23" t="n">
-        <v>2081</v>
+        <v>2099</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>46178.13067163105</v>
+        <v>46200.06533891158</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>2050</v>
+        <v>2076</v>
       </c>
       <c r="L24" t="n">
-        <v>1833</v>
+        <v>1851</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>46178.13074339613</v>
+        <v>46200.06540877344</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>2510</v>
+        <v>2540</v>
       </c>
       <c r="L25" t="n">
-        <v>2157</v>
+        <v>2176</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>46178.13080839641</v>
+        <v>46200.06547999065</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>1889</v>
+        <v>1915</v>
       </c>
       <c r="L26" t="n">
-        <v>1836</v>
+        <v>1855</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>46178.1308755404</v>
+        <v>46200.06555464987</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>1685</v>
+        <v>1711</v>
       </c>
       <c r="L27" t="n">
-        <v>1636</v>
+        <v>1655</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>46178.13093188993</v>
+        <v>46200.06561461053</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>1599</v>
+        <v>1622</v>
       </c>
       <c r="L28" t="n">
-        <v>1611</v>
+        <v>1629</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>46178.13098670004</v>
+        <v>46200.06566883281</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>1578</v>
+        <v>1603</v>
       </c>
       <c r="L29" t="n">
-        <v>1554</v>
+        <v>1571</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46178.13103780842</v>
+        <v>46200.06572052491</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         <v>9.98</v>
       </c>
       <c r="K30" t="n">
-        <v>2172</v>
+        <v>2205</v>
       </c>
       <c r="L30" t="n">
-        <v>1970</v>
+        <v>1989</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>46178.13108406728</v>
+        <v>46200.06577512756</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>1752</v>
+        <v>1778</v>
       </c>
       <c r="L31" t="n">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>46178.13115080522</v>
+        <v>46200.06584651686</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>1635</v>
+        <v>1664</v>
       </c>
       <c r="L32" t="n">
-        <v>1619</v>
+        <v>1638</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>46178.1312301471</v>
+        <v>46200.0659095857</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="L33" t="n">
-        <v>1778</v>
+        <v>1798</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>46178.13129380483</v>
+        <v>46200.06597671349</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         <v>9.98</v>
       </c>
       <c r="K34" t="n">
-        <v>1901</v>
+        <v>1931</v>
       </c>
       <c r="L34" t="n">
-        <v>1699</v>
+        <v>1721</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>46178.13135625876</v>
+        <v>46200.06604636737</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>1566</v>
+        <v>1594</v>
       </c>
       <c r="L35" t="n">
-        <v>1489</v>
+        <v>1510</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>46178.13140951812</v>
+        <v>46200.06611136001</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>1544</v>
+        <v>1573</v>
       </c>
       <c r="L36" t="n">
-        <v>1496</v>
+        <v>1523</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>46178.13145817772</v>
+        <v>46200.06616541677</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3279,10 +3279,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="L37" t="n">
-        <v>1366</v>
+        <v>1390</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>46178.13150732838</v>
+        <v>46200.06622096576</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>1335</v>
+        <v>1361</v>
       </c>
       <c r="L38" t="n">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>46178.12930367925</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>46178.13155654132</v>
+        <v>46200.06627615183</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>1356</v>
+        <v>1383</v>
       </c>
       <c r="L39" t="n">
-        <v>1301</v>
+        <v>1323</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>46178.13161038465</v>
+        <v>46200.06633496576</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>1353</v>
+        <v>1383</v>
       </c>
       <c r="L40" t="n">
-        <v>1245</v>
+        <v>1265</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>46178.13167482005</v>
+        <v>46200.06640328404</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>1626</v>
+        <v>1657</v>
       </c>
       <c r="L41" t="n">
-        <v>1357</v>
+        <v>1377</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06390598765</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>46178.131726151</v>
+        <v>46200.06645923405</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>1398</v>
+        <v>1429</v>
       </c>
       <c r="L42" t="n">
-        <v>1223</v>
+        <v>1246</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>46178.13178184134</v>
+        <v>46200.06652151935</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3741,10 +3741,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>1235</v>
+        <v>1264</v>
       </c>
       <c r="L43" t="n">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>46178.13182933854</v>
+        <v>46200.0665823235</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>1206</v>
+        <v>1236</v>
       </c>
       <c r="L44" t="n">
-        <v>1141</v>
+        <v>1163</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>46178.13187854139</v>
+        <v>46200.06663825874</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3895,10 +3895,10 @@
         <v>9.98</v>
       </c>
       <c r="K45" t="n">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="L45" t="n">
-        <v>1148</v>
+        <v>1171</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>46178.1319221446</v>
+        <v>46200.06668936562</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -3972,10 +3972,10 @@
         <v>9.98</v>
       </c>
       <c r="K46" t="n">
-        <v>1303</v>
+        <v>1332</v>
       </c>
       <c r="L46" t="n">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>46178.13199409853</v>
+        <v>46200.06675460705</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4049,10 +4049,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>1350</v>
+        <v>1384</v>
       </c>
       <c r="L47" t="n">
-        <v>1167</v>
+        <v>1192</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>46178.1320512078</v>
+        <v>46200.06681517714</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>1376</v>
+        <v>1411</v>
       </c>
       <c r="L48" t="n">
-        <v>1159</v>
+        <v>1182</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>46178.13210388397</v>
+        <v>46200.06687439705</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         <v>9.98</v>
       </c>
       <c r="K49" t="n">
-        <v>1286</v>
+        <v>1322</v>
       </c>
       <c r="L49" t="n">
-        <v>1147</v>
+        <v>1173</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="N49" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>46178.13216251698</v>
+        <v>46200.06693650451</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>1689</v>
+        <v>1729</v>
       </c>
       <c r="L50" t="n">
-        <v>1325</v>
+        <v>1355</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>46178.13221479768</v>
+        <v>46200.06699480129</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>1333</v>
+        <v>1374</v>
       </c>
       <c r="L51" t="n">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>46178.13226821603</v>
+        <v>46200.06705724817</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>1304</v>
+        <v>1342</v>
       </c>
       <c r="L52" t="n">
-        <v>1129</v>
+        <v>1168</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>46178.13232187484</v>
+        <v>46200.06711746915</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4511,10 +4511,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>1525</v>
+        <v>1567</v>
       </c>
       <c r="L53" t="n">
-        <v>1151</v>
+        <v>1191</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>46178.13237780233</v>
+        <v>46200.06718168794</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>1538</v>
+        <v>1588</v>
       </c>
       <c r="L54" t="n">
-        <v>1205</v>
+        <v>1253</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>46178.13243242368</v>
+        <v>46200.0672409242</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -4665,10 +4665,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>1537</v>
+        <v>1594</v>
       </c>
       <c r="L55" t="n">
-        <v>1173</v>
+        <v>1225</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="N55" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>46178.13249492506</v>
+        <v>46200.06730809289</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4742,10 +4742,10 @@
         <v>9.98</v>
       </c>
       <c r="K56" t="n">
-        <v>1388</v>
+        <v>1457</v>
       </c>
       <c r="L56" t="n">
-        <v>1082</v>
+        <v>1146</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>46178.13255433791</v>
+        <v>46200.06737329751</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>1156</v>
+        <v>1237</v>
       </c>
       <c r="L57" t="n">
-        <v>994</v>
+        <v>1068</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>46178.13260720635</v>
+        <v>46200.06743270584</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>1105</v>
+        <v>1260</v>
       </c>
       <c r="L58" t="n">
-        <v>957</v>
+        <v>1094</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>46178.12929471149</v>
+        <v>46200.06389698301</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>46178.13266274552</v>
+        <v>46200.06749057578</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
